--- a/output/Gym_Pano_Yukleme_Cetveli.xlsx
+++ b/output/Gym_Pano_Yukleme_Cetveli.xlsx
@@ -284,6 +284,18 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -294,18 +306,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -773,7 +773,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU  ·  Rev E  ·  17 Eylül 2026</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU  ·  Rev F  ·  17 Eylül 2026</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n">
+      <c r="K6" s="9" t="n">
         <v>280</v>
       </c>
+      <c r="L6" s="9" t="n"/>
       <c r="M6" s="10">
         <f>SUM(J6:L6)</f>
         <v/>
@@ -962,7 +962,7 @@
       <c r="G7" s="14" t="n"/>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
@@ -1009,7 +1009,7 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -1056,7 +1056,7 @@
       <c r="G9" s="14" t="n"/>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1107,7 +1107,7 @@
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -1115,10 +1115,10 @@
           <t>NHXMH</t>
         </is>
       </c>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n">
+      <c r="J10" s="9" t="n">
         <v>108</v>
       </c>
+      <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="10">
         <f>SUM(J10:L10)</f>
@@ -1158,7 +1158,7 @@
       <c r="G11" s="14" t="n"/>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -1166,10 +1166,10 @@
           <t>NHXMH</t>
         </is>
       </c>
-      <c r="J11" s="16" t="n">
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n">
         <v>64</v>
       </c>
-      <c r="K11" s="16" t="n"/>
       <c r="L11" s="16" t="n"/>
       <c r="M11" s="17">
         <f>SUM(J11:L11)</f>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Priz — salon kuzey ve batı</t>
+          <t>Priz — salon kuzey (PR12–PR16, PR1)</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       <c r="J13" s="16" t="n"/>
       <c r="K13" s="16" t="n"/>
       <c r="L13" s="16" t="n">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="M13" s="17">
         <f>SUM(J13:L13)</f>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="N13" s="18" t="inlineStr">
         <is>
-          <t>Priz — salon güney ve doğu</t>
+          <t>Priz — salon güney (PR5–PR9)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
           <t>NHXMH</t>
         </is>
       </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J14" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="10">
         <f>SUM(J14:L14)</f>
@@ -1322,14 +1322,14 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>Priz — banko, POS, veri</t>
+          <t>Priz — salon batı ve doğu (PR2–PR4, PR10, PR11)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr"/>
@@ -1359,31 +1359,27 @@
         </is>
       </c>
       <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="16" t="n">
-        <v>2400</v>
-      </c>
+      <c r="K15" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" s="16" t="n"/>
       <c r="M15" s="17">
         <f>SUM(J15:L15)</f>
         <v/>
       </c>
       <c r="N15" s="18" t="inlineStr">
         <is>
-          <t>Priz — kardiyo ekipmanı (ayrı linye)</t>
+          <t>Priz — banko, POS, veri</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>2×40 A / 30 mA, A tipi</t>
-        </is>
-      </c>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>1x16 C 6kA</t>
@@ -1409,10 +1405,10 @@
           <t>NHXMH</t>
         </is>
       </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n">
-        <v>500</v>
-      </c>
+      <c r="J16" s="9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="10">
         <f>SUM(J16:L16)</f>
@@ -1420,19 +1416,19 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>Priz — ıslak hacim IP44 (ayrı kaçak akım)</t>
+          <t>Priz — kardiyo ekipmanı (ayrı linye)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Korumasız (izlenir)</t>
+          <t>2×40 A / 30 mA, A tipi</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -1446,10 +1442,10 @@
         </is>
       </c>
       <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n">
+      <c r="F17" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="G17" s="14" t="n"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
           <t>3×2,5</t>
@@ -1463,7 +1459,7 @@
       <c r="J17" s="16" t="n"/>
       <c r="K17" s="16" t="n"/>
       <c r="L17" s="16" t="n">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="M17" s="17">
         <f>SUM(J17:L17)</f>
@@ -1471,17 +1467,21 @@
       </c>
       <c r="N17" s="18" t="inlineStr">
         <is>
-          <t>Klima — arena 24.000 BTU</t>
+          <t>Priz — ıslak hacim IP44 (ayrı kaçak akım)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>K2</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr"/>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Korumasız (izlenir)</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>1x16 C 6kA</t>
@@ -1507,10 +1507,10 @@
           <t>NHXMH</t>
         </is>
       </c>
-      <c r="J18" s="9" t="n">
-        <v>1700</v>
-      </c>
-      <c r="K18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n">
+        <v>2200</v>
+      </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="10">
         <f>SUM(J18:L18)</f>
@@ -1518,14 +1518,14 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>Klima — fonksiyonel 18.000 BTU</t>
+          <t>Klima — arena 24.000 BTU</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="16" t="n">
-        <v>1150</v>
+        <v>1700</v>
       </c>
       <c r="L19" s="16" t="n"/>
       <c r="M19" s="17">
@@ -1565,14 +1565,14 @@
       </c>
       <c r="N19" s="18" t="inlineStr">
         <is>
-          <t>Klima — giriş 12.000 BTU</t>
+          <t>Klima — fonksiyonel 18.000 BTU</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr"/>
@@ -1601,35 +1601,31 @@
           <t>NHXMH</t>
         </is>
       </c>
-      <c r="J20" s="9" t="n"/>
+      <c r="J20" s="9" t="n">
+        <v>1150</v>
+      </c>
       <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n">
-        <v>1150</v>
-      </c>
+      <c r="L20" s="9" t="n"/>
       <c r="M20" s="10">
         <f>SUM(J20:L20)</f>
         <v/>
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>Klima — dinlenme 12.000 BTU</t>
+          <t>Klima — giriş 12.000 BTU</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>2×40 A / 30 mA, A tipi</t>
-        </is>
-      </c>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>1x32 C 6kA</t>
+          <t>1x16 C 6kA</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
@@ -1644,16 +1640,16 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>3×6</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>N2XH</t>
+          <t>NHXMH</t>
         </is>
       </c>
       <c r="J21" s="16" t="n">
-        <v>6000</v>
+        <v>1150</v>
       </c>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="16" t="n"/>
@@ -1663,20 +1659,24 @@
       </c>
       <c r="N21" s="18" t="inlineStr">
         <is>
-          <t>Su ısıtıcı — erkek bloğu 6 kW</t>
+          <t>Klima — dinlenme 12.000 BTU</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2×40 A / 30 mA, A tipi</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>1x32 C 6kA</t>
+          <t>1x20 C 6kA</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1691,43 +1691,39 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>3×6</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>N2XH</t>
+          <t>NHXMH</t>
         </is>
       </c>
       <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="9" t="n">
+        <v>3000</v>
+      </c>
       <c r="M22" s="10">
         <f>SUM(J22:L22)</f>
         <v/>
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Su ısıtıcı — kadın bloğu 6 kW</t>
+          <t>Su ısıtıcı — erkek bloğu, boyler 3 kW</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>4×40 A / 30 mA, A tipi</t>
-        </is>
-      </c>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>1x10 C 6kA</t>
+          <t>1x20 C 6kA</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -1742,7 +1738,7 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -1750,31 +1746,35 @@
           <t>NHXMH</t>
         </is>
       </c>
-      <c r="J23" s="16" t="n">
-        <v>450</v>
-      </c>
+      <c r="J23" s="16" t="n"/>
       <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="16" t="n">
+        <v>3000</v>
+      </c>
       <c r="M23" s="17">
         <f>SUM(J23:L23)</f>
         <v/>
       </c>
       <c r="N23" s="18" t="inlineStr">
         <is>
-          <t>Havalandırma — taze hava + egzoz fanı</t>
+          <t>Su ısıtıcı — kadın bloğu, boyler 3 kW</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>V2</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr"/>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>4×40 A / 30 mA, A tipi</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>1x6 C 6kA</t>
+          <t>1x10 C 6kA</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="9" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="10">
@@ -1808,24 +1808,20 @@
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>Islak hacim egzoz fanı</t>
+          <t>Havalandırma — taze hava + egzoz fanı</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>Korumasız (izlenir)</t>
-        </is>
-      </c>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>1x10 C 6kA</t>
+          <t>1x6 C 6kA</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -1834,10 +1830,10 @@
         </is>
       </c>
       <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="14" t="n"/>
       <c r="H25" s="14" t="inlineStr">
         <is>
           <t>3×2,5</t>
@@ -1850,7 +1846,7 @@
       </c>
       <c r="J25" s="16" t="n"/>
       <c r="K25" s="16" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="L25" s="16" t="n"/>
       <c r="M25" s="17">
@@ -1859,20 +1855,24 @@
       </c>
       <c r="N25" s="18" t="inlineStr">
         <is>
-          <t>Zayıf akım — rack, CCTV, ses, geçiş kontrol</t>
+          <t>Islak hacim egzoz fanı</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr"/>
+          <t>Z1</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Korumasız (izlenir)</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>1x6 C 6kA</t>
+          <t>1x10 C 6kA</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1887,7 +1887,7 @@
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -1896,30 +1896,30 @@
         </is>
       </c>
       <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n">
-        <v>150</v>
-      </c>
-      <c r="L26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n">
+        <v>600</v>
+      </c>
       <c r="M26" s="10">
         <f>SUM(J26:L26)</f>
         <v/>
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>Yangın algılama paneli (kesintisiz)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr"/>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>1x16 C 6kA</t>
+          <t>Zayıf akım — rack, CCTV, ses, geçiş kontrol</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Z2</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr"/>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>1x6 C 6kA</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -1928,38 +1928,42 @@
         </is>
       </c>
       <c r="E27" s="14" t="n"/>
-      <c r="F27" s="14" t="n"/>
+      <c r="F27" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="G27" s="14" t="n"/>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>3×2,5</t>
-        </is>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>3×2,5</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>NHXMH</t>
         </is>
       </c>
-      <c r="J27" s="16" t="n"/>
+      <c r="J27" s="16" t="n">
+        <v>150</v>
+      </c>
       <c r="K27" s="16" t="n"/>
       <c r="L27" s="16" t="n"/>
-      <c r="M27" s="23">
+      <c r="M27" s="17">
         <f>SUM(J27:L27)</f>
         <v/>
       </c>
-      <c r="N27" s="24" t="inlineStr">
-        <is>
-          <t>YEDEK — ileride ilave edilecek tüketici için boş linye</t>
+      <c r="N27" s="18" t="inlineStr">
+        <is>
+          <t>Yangın algılama paneli (kesintisiz)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr"/>
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr"/>
       <c r="C28" s="8" t="inlineStr">
         <is>
           <t>1x16 C 6kA</t>
@@ -1986,23 +1990,23 @@
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
-      <c r="M28" s="27">
+      <c r="M28" s="23">
         <f>SUM(J28:L28)</f>
         <v/>
       </c>
-      <c r="N28" s="28" t="inlineStr">
+      <c r="N28" s="24" t="inlineStr">
         <is>
           <t>YEDEK — ileride ilave edilecek tüketici için boş linye</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="inlineStr"/>
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr"/>
       <c r="C29" s="15" t="inlineStr">
         <is>
           <t>1x16 C 6kA</t>
@@ -2029,23 +2033,23 @@
       <c r="J29" s="16" t="n"/>
       <c r="K29" s="16" t="n"/>
       <c r="L29" s="16" t="n"/>
-      <c r="M29" s="23">
+      <c r="M29" s="27">
         <f>SUM(J29:L29)</f>
         <v/>
       </c>
-      <c r="N29" s="24" t="inlineStr">
+      <c r="N29" s="28" t="inlineStr">
         <is>
           <t>YEDEK — ileride ilave edilecek tüketici için boş linye</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr"/>
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr"/>
       <c r="C30" s="8" t="inlineStr">
         <is>
           <t>1x16 C 6kA</t>
@@ -2072,107 +2076,124 @@
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
-      <c r="M30" s="27">
+      <c r="M30" s="23">
         <f>SUM(J30:L30)</f>
         <v/>
       </c>
-      <c r="N30" s="28" t="inlineStr">
+      <c r="N30" s="24" t="inlineStr">
         <is>
           <t>YEDEK — ileride ilave edilecek tüketici için boş linye</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr"/>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>1x16 C 6kA</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>3×2,5</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>NHXMH</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="n"/>
+      <c r="K31" s="16" t="n"/>
+      <c r="L31" s="16" t="n"/>
+      <c r="M31" s="27">
+        <f>SUM(J31:L31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="28" t="inlineStr">
+        <is>
+          <t>YEDEK — ileride ilave edilecek tüketici için boş linye</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>TOPLAM / TOTAL</t>
         </is>
       </c>
-      <c r="E31" s="29">
-        <f>SUM(E6:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="29">
-        <f>SUM(F6:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="29">
-        <f>SUM(G6:G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="29" t="inlineStr"/>
-      <c r="I31" s="29" t="inlineStr"/>
-      <c r="J31" s="30">
-        <f>SUM(J6:J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="30">
-        <f>SUM(K6:K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="30">
-        <f>SUM(L6:L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="30">
-        <f>SUM(M6:M30)</f>
-        <v/>
-      </c>
-      <c r="N31" s="31" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="E32" s="29">
+        <f>SUM(E6:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="29">
+        <f>SUM(F6:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="29">
+        <f>SUM(G6:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="29" t="inlineStr"/>
+      <c r="I32" s="29" t="inlineStr"/>
+      <c r="J32" s="30">
+        <f>SUM(J6:J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="30">
+        <f>SUM(K6:K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="30">
+        <f>SUM(L6:L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="30">
+        <f>SUM(M6:M31)</f>
+        <v/>
+      </c>
+      <c r="N32" s="31" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>PANO BİLGİLERİ</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="34" t="n"/>
-      <c r="H33" s="32" t="inlineStr">
-        <is>
-          <t>DİVERSİTE KATSAYILARI</t>
-        </is>
-      </c>
-      <c r="I33" s="33" t="n"/>
-      <c r="J33" s="33" t="n"/>
-      <c r="K33" s="33" t="n"/>
-      <c r="L33" s="33" t="n"/>
-      <c r="M33" s="33" t="n"/>
-      <c r="N33" s="34" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>PANO ADI / PANEL NAME</t>
         </is>
       </c>
       <c r="B34" s="33" t="n"/>
       <c r="C34" s="33" t="n"/>
-      <c r="D34" s="34" t="n"/>
-      <c r="E34" s="36" t="inlineStr">
-        <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="H34" s="35" t="inlineStr">
-        <is>
-          <t>Aydınlatma diversitesi</t>
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="34" t="n"/>
+      <c r="H34" s="32" t="inlineStr">
+        <is>
+          <t>DİVERSİTE KATSAYILARI</t>
         </is>
       </c>
       <c r="I34" s="33" t="n"/>
-      <c r="J34" s="34" t="n"/>
-      <c r="K34" s="37" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L34" s="34" t="n"/>
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="33" t="n"/>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="33" t="n"/>
+      <c r="N34" s="34" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="35" t="inlineStr">
         <is>
-          <t>KOLON NO / RISER NO</t>
+          <t>PANO ADI / PANEL NAME</t>
         </is>
       </c>
       <c r="B35" s="33" t="n"/>
@@ -2180,184 +2201,210 @@
       <c r="D35" s="34" t="n"/>
       <c r="E35" s="36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="H35" s="35" t="inlineStr">
         <is>
-          <t>Priz diversitesi</t>
+          <t>Aydınlatma diversitesi</t>
         </is>
       </c>
       <c r="I35" s="33" t="n"/>
       <c r="J35" s="34" t="n"/>
       <c r="K35" s="37" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L35" s="34" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="35" t="inlineStr">
         <is>
-          <t>COS φ / POWER FACTOR</t>
+          <t>KOLON NO / RISER NO</t>
         </is>
       </c>
       <c r="B36" s="33" t="n"/>
       <c r="C36" s="33" t="n"/>
       <c r="D36" s="34" t="n"/>
-      <c r="E36" s="38" t="n">
-        <v>0.9</v>
+      <c r="E36" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H36" s="35" t="inlineStr">
         <is>
-          <t>Motor / cihaz diversitesi</t>
+          <t>Priz diversitesi</t>
         </is>
       </c>
       <c r="I36" s="33" t="n"/>
       <c r="J36" s="34" t="n"/>
       <c r="K36" s="37" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L36" s="34" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1">
+    <row r="37">
       <c r="A37" s="35" t="inlineStr">
         <is>
-          <t>NOMİNAL AKIM / NOM. CURRENT [A]</t>
+          <t>COS φ / POWER FACTOR</t>
         </is>
       </c>
       <c r="B37" s="33" t="n"/>
       <c r="C37" s="33" t="n"/>
       <c r="D37" s="34" t="n"/>
-      <c r="E37" s="38">
-        <f>M31/(SQRT(3)*400*E36)</f>
-        <v/>
-      </c>
-      <c r="H37" s="18" t="inlineStr">
-        <is>
-          <t>1) Gerilim düşüm hesapları yapılarak kesitler belirlenmiştir — bkz. E-07 paftası.</t>
-        </is>
-      </c>
+      <c r="E37" s="38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H37" s="35" t="inlineStr">
+        <is>
+          <t>Motor / cihaz diversitesi</t>
+        </is>
+      </c>
+      <c r="I37" s="33" t="n"/>
+      <c r="J37" s="34" t="n"/>
+      <c r="K37" s="37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L37" s="34" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="35" t="inlineStr">
         <is>
-          <t>TALEP AKIM / DEMAND CURRENT [A]</t>
+          <t>NOMİNAL AKIM / NOM. CURRENT [A]</t>
         </is>
       </c>
       <c r="B38" s="33" t="n"/>
       <c r="C38" s="33" t="n"/>
       <c r="D38" s="34" t="n"/>
       <c r="E38" s="38">
-        <f>M43/(SQRT(3)*400*E36)</f>
+        <f>M32/(SQRT(3)*400*E37)</f>
         <v/>
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>2) Tüm son devrelerde 30 mA A tipi kaçak akım koruması; ana girişte 300 mA S tipi seçici koruma.</t>
+          <t>1) Gerilim düşüm hesapları yapılarak kesitler belirlenmiştir — bkz. E-07 paftası.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="35" t="inlineStr">
         <is>
-          <t>BESLEME KABLOSU / SUPPLY CABLE</t>
+          <t>TALEP AKIM / DEMAND CURRENT [A]</t>
         </is>
       </c>
       <c r="B39" s="33" t="n"/>
       <c r="C39" s="33" t="n"/>
       <c r="D39" s="34" t="n"/>
-      <c r="E39" s="36" t="inlineStr">
-        <is>
-          <t>NYY 5×10 mm²</t>
-        </is>
+      <c r="E39" s="38">
+        <f>M44/(SQRT(3)*400*E37)</f>
+        <v/>
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>3) Yangın algılama paneli (Z2) kaçak akım rölesi arkasına ALINMAZ; kendi aküsüyle 60 dk beslenir.</t>
+          <t>2) Tüm son devrelerde 30 mA A tipi kaçak akım koruması; ana girişte 300 mA S tipi seçici koruma.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="35" t="inlineStr">
         <is>
-          <t>IŞIK TALEP GÜCÜ / LIGHTING DEMAND [W]</t>
+          <t>BESLEME KABLOSU / SUPPLY CABLE</t>
         </is>
       </c>
       <c r="B40" s="33" t="n"/>
       <c r="C40" s="33" t="n"/>
       <c r="D40" s="34" t="n"/>
-      <c r="E40" s="39">
-        <f>SUMIF($E$6:$E$30,1,$M$6:$M$30)*K34</f>
-        <v/>
+      <c r="E40" s="36" t="inlineStr">
+        <is>
+          <t>NYY 5×10 mm²</t>
+        </is>
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>4) Kablolar halojensiz (NHXMH / N2XH); ıslak hacim linyeleri ayrı kaçak akım rölesindedir.</t>
+          <t>3) Yangın algılama paneli (Z2) kaçak akım rölesi arkasına ALINMAZ; kendi aküsüyle 60 dk beslenir.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="35" t="inlineStr">
         <is>
-          <t>PRİZ TALEP GÜCÜ / SOCKET DEMAND [W]</t>
+          <t>IŞIK TALEP GÜCÜ / LIGHTING DEMAND [W]</t>
         </is>
       </c>
       <c r="B41" s="33" t="n"/>
       <c r="C41" s="33" t="n"/>
       <c r="D41" s="34" t="n"/>
       <c r="E41" s="39">
-        <f>SUMIF($F$6:$F$30,1,$M$6:$M$30)*K35</f>
+        <f>SUMIF($E$6:$E$31,1,$M$6:$M$31)*K35</f>
         <v/>
       </c>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>5) Akım taşıma kapasiteleri TS HD 60364-5-52, B2 döşeme yöntemi, 30 °C ortam içindir.</t>
+          <t>4) Kablolar halojensiz (NHXMH / N2XH); ıslak hacim linyeleri ayrı kaçak akım rölesindedir.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="35" t="inlineStr">
         <is>
-          <t>MOTOR TALEP GÜCÜ / MOTOR DEMAND [W]</t>
+          <t>PRİZ TALEP GÜCÜ / SOCKET DEMAND [W]</t>
         </is>
       </c>
       <c r="B42" s="33" t="n"/>
       <c r="C42" s="33" t="n"/>
       <c r="D42" s="34" t="n"/>
       <c r="E42" s="39">
-        <f>SUMIF($G$6:$G$30,1,$M$6:$M$30)*K36</f>
+        <f>SUMIF($F$6:$F$31,1,$M$6:$M$31)*K36</f>
         <v/>
       </c>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>6) Pano içinde en az 4 adet yedek linye yeri bırakılacaktır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
+          <t>5) Akım taşıma kapasiteleri TS HD 60364-5-52, B2 döşeme yöntemi, 30 °C ortam içindir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" s="35" t="inlineStr">
         <is>
-          <t>TOPLAM TALEP GÜCÜ / TOTAL DEMAND [W]</t>
+          <t>MOTOR TALEP GÜCÜ / MOTOR DEMAND [W]</t>
         </is>
       </c>
       <c r="B43" s="33" t="n"/>
       <c r="C43" s="33" t="n"/>
       <c r="D43" s="34" t="n"/>
       <c r="E43" s="39">
-        <f>SUM(E40:E42)</f>
-        <v/>
+        <f>SUMIF($G$6:$G$31,1,$M$6:$M$31)*K37</f>
+        <v/>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>6) Pano içinde en az 4 adet yedek linye yeri bırakılacaktır.</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="35" t="inlineStr">
         <is>
-          <t>GİRİŞ ŞALTERİ / MAIN CIRCUIT BREAKER</t>
+          <t>TOPLAM TALEP GÜCÜ / TOTAL DEMAND [W]</t>
         </is>
       </c>
       <c r="B44" s="33" t="n"/>
       <c r="C44" s="33" t="n"/>
       <c r="D44" s="34" t="n"/>
-      <c r="E44" s="36" t="inlineStr">
+      <c r="E44" s="39">
+        <f>SUM(E41:E43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>GİRİŞ ŞALTERİ / MAIN CIRCUIT BREAKER</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="n"/>
+      <c r="C45" s="33" t="n"/>
+      <c r="D45" s="34" t="n"/>
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>3x32A TMŞ</t>
         </is>
@@ -2366,8 +2413,6 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="E43:F43"/>
-    <mergeCell ref="H37:N37"/>
-    <mergeCell ref="K34:L34"/>
     <mergeCell ref="H36:J36"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A38:D38"/>
@@ -2378,18 +2423,16 @@
     <mergeCell ref="E39:F39"/>
     <mergeCell ref="D5"/>
     <mergeCell ref="H42:N42"/>
-    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="E44:F44"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A33:F33"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="K35:L35"/>
     <mergeCell ref="E38:F38"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="H37:J37"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="H43:N43"/>
     <mergeCell ref="J5"/>
     <mergeCell ref="H38:N38"/>
     <mergeCell ref="K5"/>
@@ -2398,7 +2441,7 @@
     <mergeCell ref="C5"/>
     <mergeCell ref="A36:D36"/>
     <mergeCell ref="E5"/>
-    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="H41:N41"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="H40:N40"/>
@@ -2406,6 +2449,9 @@
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="H39:N39"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="H35:J35"/>
@@ -2417,9 +2463,10 @@
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="E37:F37"/>
+    <mergeCell ref="K37:L37"/>
     <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H34:J34"/>
     <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -2434,7 +2481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2552,7 +2599,7 @@
       </c>
       <c r="C5" s="45" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D5" s="46" t="n">
@@ -2572,20 +2619,20 @@
       </c>
       <c r="I5" s="45" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J5" s="46" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="K5" s="46" t="n">
         <v>13.5</v>
       </c>
       <c r="L5" s="46" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M5" s="49" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="N5" s="50" t="inlineStr">
         <is>
@@ -2626,20 +2673,20 @@
       </c>
       <c r="I6" s="45" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J6" s="46" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="K6" s="46" t="n">
         <v>11.2</v>
       </c>
       <c r="L6" s="46" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M6" s="49" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="N6" s="50" t="inlineStr">
         <is>
@@ -2680,20 +2727,20 @@
       </c>
       <c r="I7" s="45" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J7" s="46" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="K7" s="46" t="n">
         <v>13.9</v>
       </c>
       <c r="L7" s="46" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M7" s="49" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="N7" s="50" t="inlineStr">
         <is>
@@ -2734,11 +2781,11 @@
       </c>
       <c r="I8" s="45" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J8" s="46" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="K8" s="46" t="n">
         <v>12</v>
@@ -2747,7 +2794,7 @@
         <v>0.1</v>
       </c>
       <c r="M8" s="49" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="N8" s="50" t="inlineStr">
         <is>
@@ -2768,7 +2815,7 @@
       </c>
       <c r="C9" s="45" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D9" s="46" t="n">
@@ -2788,20 +2835,20 @@
       </c>
       <c r="I9" s="45" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J9" s="46" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="K9" s="46" t="n">
         <v>16.3</v>
       </c>
       <c r="L9" s="46" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M9" s="49" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="N9" s="50" t="inlineStr">
         <is>
@@ -2822,7 +2869,7 @@
       </c>
       <c r="C10" s="45" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D10" s="46" t="n">
@@ -2842,11 +2889,11 @@
       </c>
       <c r="I10" s="45" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J10" s="46" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="K10" s="46" t="n">
         <v>10</v>
@@ -2855,7 +2902,7 @@
         <v>0.1</v>
       </c>
       <c r="M10" s="49" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="N10" s="50" t="inlineStr">
         <is>
@@ -2871,7 +2918,7 @@
       </c>
       <c r="B11" s="44" t="inlineStr">
         <is>
-          <t>Priz — salon kuzey ve batı</t>
+          <t>Priz — salon kuzey (PR12–PR16, PR1)</t>
         </is>
       </c>
       <c r="C11" s="45" t="inlineStr">
@@ -2880,16 +2927,16 @@
         </is>
       </c>
       <c r="D11" s="46" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E11" s="46" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="F11" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="G11" s="46" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="H11" s="48" t="n">
         <v>16</v>
@@ -2903,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="K11" s="46" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="L11" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M11" s="49" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="N11" s="50" t="inlineStr">
         <is>
@@ -2925,7 +2972,7 @@
       </c>
       <c r="B12" s="44" t="inlineStr">
         <is>
-          <t>Priz — salon güney ve doğu</t>
+          <t>Priz — salon güney (PR5–PR9)</t>
         </is>
       </c>
       <c r="C12" s="45" t="inlineStr">
@@ -2934,16 +2981,16 @@
         </is>
       </c>
       <c r="D12" s="46" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="E12" s="46" t="n">
-        <v>0.6</v>
+        <v>0.375</v>
       </c>
       <c r="F12" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="G12" s="46" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="H12" s="48" t="n">
         <v>16</v>
@@ -2960,10 +3007,10 @@
         <v>16.5</v>
       </c>
       <c r="L12" s="46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M12" s="49" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="N12" s="50" t="inlineStr">
         <is>
@@ -2974,30 +3021,30 @@
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B13" s="44" t="inlineStr">
         <is>
-          <t>Priz — banko, POS, veri</t>
+          <t>Priz — salon batı ve doğu (PR2–PR4, PR10, PR11)</t>
         </is>
       </c>
       <c r="C13" s="45" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D13" s="46" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E13" s="46" t="n">
-        <v>0.7</v>
+        <v>0.375</v>
       </c>
       <c r="F13" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="G13" s="46" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="H13" s="48" t="n">
         <v>16</v>
@@ -3011,13 +3058,13 @@
         <v>23</v>
       </c>
       <c r="K13" s="46" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="L13" s="46" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M13" s="49" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="N13" s="50" t="inlineStr">
         <is>
@@ -3028,30 +3075,30 @@
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B14" s="44" t="inlineStr">
         <is>
-          <t>Priz — kardiyo ekipmanı (ayrı linye)</t>
+          <t>Priz — banko, POS, veri</t>
         </is>
       </c>
       <c r="C14" s="45" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D14" s="46" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="46" t="n">
-        <v>1.92</v>
+        <v>0.7</v>
       </c>
       <c r="F14" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="G14" s="46" t="n">
-        <v>11.6</v>
+        <v>4.8</v>
       </c>
       <c r="H14" s="48" t="n">
         <v>16</v>
@@ -3065,13 +3112,13 @@
         <v>23</v>
       </c>
       <c r="K14" s="46" t="n">
-        <v>17.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L14" s="46" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="M14" s="49" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="N14" s="50" t="inlineStr">
         <is>
@@ -3082,30 +3129,30 @@
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B15" s="44" t="inlineStr">
         <is>
-          <t>Priz — ıslak hacim IP44 (ayrı kaçak akım)</t>
+          <t>Priz — kardiyo ekipmanı (ayrı linye)</t>
         </is>
       </c>
       <c r="C15" s="45" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D15" s="46" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="E15" s="46" t="n">
-        <v>0.15</v>
+        <v>1.92</v>
       </c>
       <c r="F15" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="G15" s="46" t="n">
-        <v>2.4</v>
+        <v>11.6</v>
       </c>
       <c r="H15" s="48" t="n">
         <v>16</v>
@@ -3119,13 +3166,13 @@
         <v>23</v>
       </c>
       <c r="K15" s="46" t="n">
-        <v>16</v>
+        <v>17.2</v>
       </c>
       <c r="L15" s="46" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="M15" s="49" t="n">
-        <v>0.27</v>
+        <v>1.4</v>
       </c>
       <c r="N15" s="50" t="inlineStr">
         <is>
@@ -3136,12 +3183,12 @@
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B16" s="44" t="inlineStr">
         <is>
-          <t>Klima — arena 24.000 BTU</t>
+          <t>Priz — ıslak hacim IP44 (ayrı kaçak akım)</t>
         </is>
       </c>
       <c r="C16" s="45" t="inlineStr">
@@ -3150,16 +3197,16 @@
         </is>
       </c>
       <c r="D16" s="46" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="E16" s="46" t="n">
-        <v>1.87</v>
+        <v>0.15</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G16" s="46" t="n">
-        <v>11.3</v>
+        <v>2.4</v>
       </c>
       <c r="H16" s="48" t="n">
         <v>16</v>
@@ -3173,13 +3220,13 @@
         <v>23</v>
       </c>
       <c r="K16" s="46" t="n">
-        <v>17.7</v>
+        <v>16</v>
       </c>
       <c r="L16" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="M16" s="49" t="n">
-        <v>1.32</v>
+        <v>0.27</v>
       </c>
       <c r="N16" s="50" t="inlineStr">
         <is>
@@ -3190,30 +3237,30 @@
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B17" s="44" t="inlineStr">
         <is>
-          <t>Klima — fonksiyonel 18.000 BTU</t>
+          <t>Klima — arena 24.000 BTU</t>
         </is>
       </c>
       <c r="C17" s="45" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D17" s="46" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="E17" s="46" t="n">
-        <v>1.445</v>
+        <v>1.87</v>
       </c>
       <c r="F17" s="47" t="n">
         <v>0.85</v>
       </c>
       <c r="G17" s="46" t="n">
-        <v>8.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="H17" s="48" t="n">
         <v>16</v>
@@ -3227,13 +3274,13 @@
         <v>23</v>
       </c>
       <c r="K17" s="46" t="n">
-        <v>12.6</v>
+        <v>17.7</v>
       </c>
       <c r="L17" s="46" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="M17" s="49" t="n">
-        <v>0.73</v>
+        <v>1.32</v>
       </c>
       <c r="N17" s="50" t="inlineStr">
         <is>
@@ -3244,12 +3291,12 @@
     <row r="18">
       <c r="A18" s="43" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B18" s="44" t="inlineStr">
         <is>
-          <t>Klima — giriş 12.000 BTU</t>
+          <t>Klima — fonksiyonel 18.000 BTU</t>
         </is>
       </c>
       <c r="C18" s="45" t="inlineStr">
@@ -3258,16 +3305,16 @@
         </is>
       </c>
       <c r="D18" s="46" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="E18" s="46" t="n">
-        <v>0.977</v>
+        <v>1.445</v>
       </c>
       <c r="F18" s="47" t="n">
         <v>0.85</v>
       </c>
       <c r="G18" s="46" t="n">
-        <v>5.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H18" s="48" t="n">
         <v>16</v>
@@ -3281,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="K18" s="46" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="L18" s="46" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="M18" s="49" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="N18" s="50" t="inlineStr">
         <is>
@@ -3298,24 +3345,24 @@
     <row r="19">
       <c r="A19" s="43" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B19" s="44" t="inlineStr">
         <is>
-          <t>Klima — dinlenme 12.000 BTU</t>
+          <t>Klima — giriş 12.000 BTU</t>
         </is>
       </c>
       <c r="C19" s="45" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D19" s="46" t="n">
         <v>1.15</v>
       </c>
       <c r="E19" s="46" t="n">
-        <v>0.805</v>
+        <v>0.977</v>
       </c>
       <c r="F19" s="47" t="n">
         <v>0.85</v>
@@ -3335,13 +3382,13 @@
         <v>23</v>
       </c>
       <c r="K19" s="46" t="n">
-        <v>14.7</v>
+        <v>12.2</v>
       </c>
       <c r="L19" s="46" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="M19" s="49" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="N19" s="50" t="inlineStr">
         <is>
@@ -3352,12 +3399,12 @@
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B20" s="44" t="inlineStr">
         <is>
-          <t>Su ısıtıcı — erkek bloğu 6 kW</t>
+          <t>Klima — dinlenme 12.000 BTU</t>
         </is>
       </c>
       <c r="C20" s="45" t="inlineStr">
@@ -3366,36 +3413,36 @@
         </is>
       </c>
       <c r="D20" s="46" t="n">
-        <v>6</v>
+        <v>1.15</v>
       </c>
       <c r="E20" s="46" t="n">
-        <v>3</v>
+        <v>0.805</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="G20" s="46" t="n">
-        <v>26.1</v>
+        <v>5.9</v>
       </c>
       <c r="H20" s="48" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I20" s="45" t="inlineStr">
         <is>
-          <t>3×6</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J20" s="46" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K20" s="46" t="n">
-        <v>16.2</v>
+        <v>14.7</v>
       </c>
       <c r="L20" s="46" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="M20" s="49" t="n">
-        <v>1.38</v>
+        <v>0.58</v>
       </c>
       <c r="N20" s="50" t="inlineStr">
         <is>
@@ -3406,50 +3453,50 @@
     <row r="21">
       <c r="A21" s="43" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B21" s="44" t="inlineStr">
         <is>
-          <t>Su ısıtıcı — kadın bloğu 6 kW</t>
+          <t>Su ısıtıcı — erkek bloğu, boyler 3 kW</t>
         </is>
       </c>
       <c r="C21" s="45" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="D21" s="46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E21" s="46" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="F21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="46" t="n">
-        <v>26.1</v>
+        <v>13</v>
       </c>
       <c r="H21" s="48" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I21" s="45" t="inlineStr">
         <is>
-          <t>3×6</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J21" s="46" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K21" s="46" t="n">
-        <v>19.3</v>
+        <v>16.2</v>
       </c>
       <c r="L21" s="46" t="n">
         <v>3.8</v>
       </c>
       <c r="M21" s="49" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="N21" s="50" t="inlineStr">
         <is>
@@ -3460,50 +3507,50 @@
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B22" s="44" t="inlineStr">
         <is>
-          <t>Havalandırma — taze hava + egzoz fanı</t>
+          <t>Su ısıtıcı — kadın bloğu, boyler 3 kW</t>
         </is>
       </c>
       <c r="C22" s="45" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="D22" s="46" t="n">
-        <v>0.45</v>
+        <v>3</v>
       </c>
       <c r="E22" s="46" t="n">
-        <v>0.45</v>
+        <v>1.8</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="G22" s="46" t="n">
-        <v>2.3</v>
+        <v>13</v>
       </c>
       <c r="H22" s="48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I22" s="45" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J22" s="46" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="K22" s="46" t="n">
-        <v>13.8</v>
+        <v>19.3</v>
       </c>
       <c r="L22" s="46" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="M22" s="49" t="n">
-        <v>0.35</v>
+        <v>1.97</v>
       </c>
       <c r="N22" s="50" t="inlineStr">
         <is>
@@ -3514,12 +3561,12 @@
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B23" s="44" t="inlineStr">
         <is>
-          <t>Islak hacim egzoz fanı</t>
+          <t>Havalandırma — taze hava + egzoz fanı</t>
         </is>
       </c>
       <c r="C23" s="45" t="inlineStr">
@@ -3528,36 +3575,36 @@
         </is>
       </c>
       <c r="D23" s="46" t="n">
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="E23" s="46" t="n">
-        <v>0.096</v>
+        <v>0.45</v>
       </c>
       <c r="F23" s="47" t="n">
         <v>0.85</v>
       </c>
       <c r="G23" s="46" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="H23" s="48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I23" s="45" t="inlineStr">
         <is>
-          <t>3×1,5</t>
+          <t>3×2,5</t>
         </is>
       </c>
       <c r="J23" s="46" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="K23" s="46" t="n">
-        <v>16.4</v>
+        <v>13.8</v>
       </c>
       <c r="L23" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M23" s="49" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="N23" s="50" t="inlineStr">
         <is>
@@ -3568,12 +3615,12 @@
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
         <is>
-          <t>Z1</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="B24" s="44" t="inlineStr">
         <is>
-          <t>Zayıf akım — rack, CCTV, ses, geçiş kontrol</t>
+          <t>Islak hacim egzoz fanı</t>
         </is>
       </c>
       <c r="C24" s="45" t="inlineStr">
@@ -3582,19 +3629,19 @@
         </is>
       </c>
       <c r="D24" s="46" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E24" s="46" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="F24" s="47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G24" s="46" t="n">
         <v>0.6</v>
       </c>
-      <c r="E24" s="46" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="F24" s="47" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G24" s="46" t="n">
-        <v>2.9</v>
-      </c>
       <c r="H24" s="48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I24" s="45" t="inlineStr">
         <is>
@@ -3605,13 +3652,13 @@
         <v>23</v>
       </c>
       <c r="K24" s="46" t="n">
-        <v>8.9</v>
+        <v>16.4</v>
       </c>
       <c r="L24" s="46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M24" s="49" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N24" s="50" t="inlineStr">
         <is>
@@ -3622,99 +3669,153 @@
     <row r="25">
       <c r="A25" s="43" t="inlineStr">
         <is>
-          <t>Z2</t>
+          <t>Z1</t>
         </is>
       </c>
       <c r="B25" s="44" t="inlineStr">
         <is>
-          <t>Yangın algılama paneli (kesintisiz)</t>
+          <t>Zayıf akım — rack, CCTV, ses, geçiş kontrol</t>
         </is>
       </c>
       <c r="C25" s="45" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="D25" s="46" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="E25" s="46" t="n">
-        <v>0.15</v>
+        <v>0.54</v>
       </c>
       <c r="F25" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="G25" s="46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H25" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="45" t="inlineStr">
+        <is>
+          <t>3×2,5</t>
+        </is>
+      </c>
+      <c r="J25" s="46" t="n">
+        <v>23</v>
+      </c>
+      <c r="K25" s="46" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L25" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M25" s="49" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N25" s="50" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Z2</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>Yangın algılama paneli (kesintisiz)</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E26" s="46" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F26" s="47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G26" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="H25" s="48" t="n">
+      <c r="H26" s="48" t="n">
         <v>6</v>
       </c>
-      <c r="I25" s="45" t="inlineStr">
-        <is>
-          <t>3×1,5</t>
-        </is>
-      </c>
-      <c r="J25" s="46" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K25" s="46" t="n">
+      <c r="I26" s="45" t="inlineStr">
+        <is>
+          <t>3×2,5</t>
+        </is>
+      </c>
+      <c r="J26" s="46" t="n">
+        <v>23</v>
+      </c>
+      <c r="K26" s="46" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="L25" s="46" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M25" s="49" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="N25" s="50" t="inlineStr">
+      <c r="L26" s="46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M26" s="49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N26" s="50" t="inlineStr">
         <is>
           <t>UYGUN</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="D26" s="51">
-        <f>SUM(D5:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="51">
-        <f>SUM(E5:E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="29" t="inlineStr"/>
-      <c r="G26" s="29" t="inlineStr"/>
-      <c r="H26" s="29" t="inlineStr"/>
-      <c r="I26" s="29" t="inlineStr"/>
-      <c r="J26" s="29" t="inlineStr"/>
-      <c r="K26" s="29" t="inlineStr"/>
-      <c r="L26" s="29" t="inlineStr"/>
-      <c r="M26" s="51">
-        <f>MAX(M5:M25)</f>
-        <v/>
-      </c>
-      <c r="N26" s="52" t="inlineStr">
+      <c r="D27" s="51">
+        <f>SUM(D5:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="51">
+        <f>SUM(E5:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="29" t="inlineStr"/>
+      <c r="G27" s="29" t="inlineStr"/>
+      <c r="H27" s="29" t="inlineStr"/>
+      <c r="I27" s="29" t="inlineStr"/>
+      <c r="J27" s="29" t="inlineStr"/>
+      <c r="K27" s="29" t="inlineStr"/>
+      <c r="L27" s="29" t="inlineStr"/>
+      <c r="M27" s="51">
+        <f>MAX(M5:M26)</f>
+        <v/>
+      </c>
+      <c r="N27" s="52" t="inlineStr">
         <is>
           <t>maks ΔU</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="53" t="inlineStr">
-        <is>
-          <t>Ana besleme: NYY 5×10 mm², 25 m, Ib = 26,7 A, In = 3×32 A, ΔU = %0,60. En uzak tüketicide toplam gerilim düşümü %2,24 — TS HD 60364-5-52'nin %5 sınırının altındadır. Faz dengesizliği %0,2.</t>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="53" t="inlineStr">
+        <is>
+          <t>Ana besleme: NYY 5×10 mm², 25 m, Ib = 23,0 A, In = 3×32 A, ΔU = %0,52. En uzak tüketicide toplam gerilim düşümü %2,49 — TS HD 60364-5-52'nin %5 sınırının altındadır. Faz dengesizliği %1,0.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A28:N28"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/output/Gym_Pano_Yukleme_Cetveli.xlsx
+++ b/output/Gym_Pano_Yukleme_Cetveli.xlsx
@@ -773,7 +773,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU  ·  Rev F  ·  17 Eylül 2026</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU  ·  Rev G  ·  17 Eylül 2026</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Korumasız (izlenir)</t>
+          <t>4×40 A / 30 mA, A tipi</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1916,7 +1916,11 @@
           <t>Z2</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr"/>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Korumasız (izlenir)</t>
+        </is>
+      </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
           <t>1x6 C 6kA</t>

--- a/output/Gym_Pano_Yukleme_Cetveli.xlsx
+++ b/output/Gym_Pano_Yukleme_Cetveli.xlsx
@@ -773,7 +773,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU  ·  Rev G  ·  17 Eylül 2026</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU  ·  Rev H  ·  17 Eylül 2026</t>
         </is>
       </c>
     </row>

--- a/output/Gym_Pano_Yukleme_Cetveli.xlsx
+++ b/output/Gym_Pano_Yukleme_Cetveli.xlsx
@@ -2684,7 +2684,7 @@
         <v>23</v>
       </c>
       <c r="K6" s="46" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="L6" s="46" t="n">
         <v>0.1</v>
@@ -2738,7 +2738,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="46" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="L7" s="46" t="n">
         <v>0.1</v>
@@ -2900,7 +2900,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="46" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="L10" s="46" t="n">
         <v>0.1</v>
@@ -3008,7 +3008,7 @@
         <v>23</v>
       </c>
       <c r="K12" s="46" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="L12" s="46" t="n">
         <v>1</v>
@@ -3116,7 +3116,7 @@
         <v>23</v>
       </c>
       <c r="K14" s="46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L14" s="46" t="n">
         <v>0.7</v>
@@ -3332,7 +3332,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="46" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="L18" s="46" t="n">
         <v>1.7</v>
@@ -3440,7 +3440,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="46" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="L20" s="46" t="n">
         <v>1.3</v>
@@ -3494,13 +3494,13 @@
         <v>23</v>
       </c>
       <c r="K21" s="46" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="L21" s="46" t="n">
         <v>3.8</v>
       </c>
       <c r="M21" s="49" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="N21" s="50" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="46" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="L24" s="46" t="n">
         <v>0.2</v>
@@ -3764,7 +3764,7 @@
         <v>23</v>
       </c>
       <c r="K26" s="46" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L26" s="46" t="n">
         <v>0.1</v>
